--- a/data/choosing-the-right-test--clinic_visits.xlsx
+++ b/data/choosing-the-right-test--clinic_visits.xlsx
@@ -6499,7 +6499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WHAT IS CAPTURED: a mixed clinic dataset for PRACTICING test selection.</t>
+          <t>WHAT IS CAPTURED: a mixed clinic dataset for PRACTICING test selection (a realistic teaching dataset written for the book).</t>
         </is>
       </c>
     </row>
